--- a/data/processed/Sector Risk Multiplier.xlsx
+++ b/data/processed/Sector Risk Multiplier.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{C119449E-6502-3D40-900F-2253E9344213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DF10385-120A-2A45-93B7-7AA9827A85D3}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{39628D33-4669-BF42-B458-9D95EBDC9FA0}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="18000" xr2:uid="{39628D33-4669-BF42-B458-9D95EBDC9FA0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sector Risk Multiplier" sheetId="1" r:id="rId1"/>
@@ -493,7 +493,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="11">
     <dxf>
@@ -801,10 +801,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1237,11 +1233,11 @@
         <v>Moderately high risk</v>
       </c>
       <c r="G5" s="8">
-        <f>IF(F5="Very low risk",1,IF(F5="Low risk",2,IF(F5="Intermediate risk",3,IF(F5="Moderately high risk",4,IF(F5="High risk",5,IF(F5="Very high risk",6, ""))))))</f>
+        <f t="shared" ref="G5:G29" si="0">IF(F5="Very low risk",1,IF(F5="Low risk",2,IF(F5="Intermediate risk",3,IF(F5="Moderately high risk",4,IF(F5="High risk",5,IF(F5="Very high risk",6, ""))))))</f>
         <v>4</v>
       </c>
       <c r="H5" s="7">
-        <f>IF(F5="Very low risk",0.75,IF(F5="Low risk",0.85,IF(F5="Intermediate risk",1,IF(F5="Moderately high risk",1.1,IF(F5="High risk",1.15,IF(F5="Very high risk",1.25, ""))))))</f>
+        <f t="shared" ref="H5:H29" si="1">IF(F5="Very low risk",0.75,IF(F5="Low risk",0.85,IF(F5="Intermediate risk",1,IF(F5="Moderately high risk",1.1,IF(F5="High risk",1.15,IF(F5="Very high risk",1.25, ""))))))</f>
         <v>1.1000000000000001</v>
       </c>
       <c r="I5"/>
@@ -1265,11 +1261,11 @@
         <v>Intermediate risk</v>
       </c>
       <c r="G6" s="8">
-        <f>IF(F6="Very low risk",1,IF(F6="Low risk",2,IF(F6="Intermediate risk",3,IF(F6="Moderately high risk",4,IF(F6="High risk",5,IF(F6="Very high risk",6, ""))))))</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="H6" s="7">
-        <f>IF(F6="Very low risk",0.75,IF(F6="Low risk",0.85,IF(F6="Intermediate risk",1,IF(F6="Moderately high risk",1.1,IF(F6="High risk",1.15,IF(F6="Very high risk",1.25, ""))))))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="I6"/>
@@ -1293,11 +1289,11 @@
         <v>Moderately high risk</v>
       </c>
       <c r="G7" s="8">
-        <f>IF(F7="Very low risk",1,IF(F7="Low risk",2,IF(F7="Intermediate risk",3,IF(F7="Moderately high risk",4,IF(F7="High risk",5,IF(F7="Very high risk",6, ""))))))</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="H7" s="7">
-        <f>IF(F7="Very low risk",0.75,IF(F7="Low risk",0.85,IF(F7="Intermediate risk",1,IF(F7="Moderately high risk",1.1,IF(F7="High risk",1.15,IF(F7="Very high risk",1.25, ""))))))</f>
+        <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="I7"/>
@@ -1321,11 +1317,11 @@
         <v>Moderately high risk</v>
       </c>
       <c r="G8" s="8">
-        <f>IF(F8="Very low risk",1,IF(F8="Low risk",2,IF(F8="Intermediate risk",3,IF(F8="Moderately high risk",4,IF(F8="High risk",5,IF(F8="Very high risk",6, ""))))))</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="H8" s="7">
-        <f>IF(F8="Very low risk",0.75,IF(F8="Low risk",0.85,IF(F8="Intermediate risk",1,IF(F8="Moderately high risk",1.1,IF(F8="High risk",1.15,IF(F8="Very high risk",1.25, ""))))))</f>
+        <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="I8"/>
@@ -1349,11 +1345,11 @@
         <v>Moderately high risk</v>
       </c>
       <c r="G9" s="8">
-        <f>IF(F9="Very low risk",1,IF(F9="Low risk",2,IF(F9="Intermediate risk",3,IF(F9="Moderately high risk",4,IF(F9="High risk",5,IF(F9="Very high risk",6, ""))))))</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="H9" s="7">
-        <f>IF(F9="Very low risk",0.75,IF(F9="Low risk",0.85,IF(F9="Intermediate risk",1,IF(F9="Moderately high risk",1.1,IF(F9="High risk",1.15,IF(F9="Very high risk",1.25, ""))))))</f>
+        <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="I9"/>
@@ -1377,11 +1373,11 @@
         <v>Low risk</v>
       </c>
       <c r="G10" s="8">
-        <f>IF(F10="Very low risk",1,IF(F10="Low risk",2,IF(F10="Intermediate risk",3,IF(F10="Moderately high risk",4,IF(F10="High risk",5,IF(F10="Very high risk",6, ""))))))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="H10" s="7">
-        <f>IF(F10="Very low risk",0.75,IF(F10="Low risk",0.85,IF(F10="Intermediate risk",1,IF(F10="Moderately high risk",1.1,IF(F10="High risk",1.15,IF(F10="Very high risk",1.25, ""))))))</f>
+        <f t="shared" si="1"/>
         <v>0.85</v>
       </c>
       <c r="I10"/>
@@ -1405,11 +1401,11 @@
         <v>Moderately high risk</v>
       </c>
       <c r="G11" s="8">
-        <f>IF(F11="Very low risk",1,IF(F11="Low risk",2,IF(F11="Intermediate risk",3,IF(F11="Moderately high risk",4,IF(F11="High risk",5,IF(F11="Very high risk",6, ""))))))</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="H11" s="7">
-        <f>IF(F11="Very low risk",0.75,IF(F11="Low risk",0.85,IF(F11="Intermediate risk",1,IF(F11="Moderately high risk",1.1,IF(F11="High risk",1.15,IF(F11="Very high risk",1.25, ""))))))</f>
+        <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="I11"/>
@@ -1433,11 +1429,11 @@
         <v>Moderately high risk</v>
       </c>
       <c r="G12" s="8">
-        <f>IF(F12="Very low risk",1,IF(F12="Low risk",2,IF(F12="Intermediate risk",3,IF(F12="Moderately high risk",4,IF(F12="High risk",5,IF(F12="Very high risk",6, ""))))))</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="H12" s="7">
-        <f>IF(F12="Very low risk",0.75,IF(F12="Low risk",0.85,IF(F12="Intermediate risk",1,IF(F12="Moderately high risk",1.1,IF(F12="High risk",1.15,IF(F12="Very high risk",1.25, ""))))))</f>
+        <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="I12"/>
@@ -1461,11 +1457,11 @@
         <v>Moderately high risk</v>
       </c>
       <c r="G13" s="8">
-        <f>IF(F13="Very low risk",1,IF(F13="Low risk",2,IF(F13="Intermediate risk",3,IF(F13="Moderately high risk",4,IF(F13="High risk",5,IF(F13="Very high risk",6, ""))))))</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="H13" s="7">
-        <f>IF(F13="Very low risk",0.75,IF(F13="Low risk",0.85,IF(F13="Intermediate risk",1,IF(F13="Moderately high risk",1.1,IF(F13="High risk",1.15,IF(F13="Very high risk",1.25, ""))))))</f>
+        <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="I13"/>
@@ -1489,11 +1485,11 @@
         <v>Low risk</v>
       </c>
       <c r="G14" s="8">
-        <f>IF(F14="Very low risk",1,IF(F14="Low risk",2,IF(F14="Intermediate risk",3,IF(F14="Moderately high risk",4,IF(F14="High risk",5,IF(F14="Very high risk",6, ""))))))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="H14" s="7">
-        <f>IF(F14="Very low risk",0.75,IF(F14="Low risk",0.85,IF(F14="Intermediate risk",1,IF(F14="Moderately high risk",1.1,IF(F14="High risk",1.15,IF(F14="Very high risk",1.25, ""))))))</f>
+        <f t="shared" si="1"/>
         <v>0.85</v>
       </c>
       <c r="I14"/>
@@ -1517,11 +1513,11 @@
         <v>Intermediate risk</v>
       </c>
       <c r="G15" s="8">
-        <f>IF(F15="Very low risk",1,IF(F15="Low risk",2,IF(F15="Intermediate risk",3,IF(F15="Moderately high risk",4,IF(F15="High risk",5,IF(F15="Very high risk",6, ""))))))</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="H15" s="7">
-        <f>IF(F15="Very low risk",0.75,IF(F15="Low risk",0.85,IF(F15="Intermediate risk",1,IF(F15="Moderately high risk",1.1,IF(F15="High risk",1.15,IF(F15="Very high risk",1.25, ""))))))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="I15"/>
@@ -1545,11 +1541,11 @@
         <v>Intermediate risk</v>
       </c>
       <c r="G16" s="8">
-        <f>IF(F16="Very low risk",1,IF(F16="Low risk",2,IF(F16="Intermediate risk",3,IF(F16="Moderately high risk",4,IF(F16="High risk",5,IF(F16="Very high risk",6, ""))))))</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="H16" s="7">
-        <f>IF(F16="Very low risk",0.75,IF(F16="Low risk",0.85,IF(F16="Intermediate risk",1,IF(F16="Moderately high risk",1.1,IF(F16="High risk",1.15,IF(F16="Very high risk",1.25, ""))))))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="I16"/>
@@ -1573,11 +1569,11 @@
         <v>Intermediate risk</v>
       </c>
       <c r="G17" s="8">
-        <f>IF(F17="Very low risk",1,IF(F17="Low risk",2,IF(F17="Intermediate risk",3,IF(F17="Moderately high risk",4,IF(F17="High risk",5,IF(F17="Very high risk",6, ""))))))</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="H17" s="7">
-        <f>IF(F17="Very low risk",0.75,IF(F17="Low risk",0.85,IF(F17="Intermediate risk",1,IF(F17="Moderately high risk",1.1,IF(F17="High risk",1.15,IF(F17="Very high risk",1.25, ""))))))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="I17"/>
@@ -1601,11 +1597,11 @@
         <v>Low risk</v>
       </c>
       <c r="G18" s="8">
-        <f>IF(F18="Very low risk",1,IF(F18="Low risk",2,IF(F18="Intermediate risk",3,IF(F18="Moderately high risk",4,IF(F18="High risk",5,IF(F18="Very high risk",6, ""))))))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="H18" s="7">
-        <f>IF(F18="Very low risk",0.75,IF(F18="Low risk",0.85,IF(F18="Intermediate risk",1,IF(F18="Moderately high risk",1.1,IF(F18="High risk",1.15,IF(F18="Very high risk",1.25, ""))))))</f>
+        <f t="shared" si="1"/>
         <v>0.85</v>
       </c>
       <c r="I18"/>
@@ -1629,11 +1625,11 @@
         <v>Moderately high risk</v>
       </c>
       <c r="G19" s="8">
-        <f>IF(F19="Very low risk",1,IF(F19="Low risk",2,IF(F19="Intermediate risk",3,IF(F19="Moderately high risk",4,IF(F19="High risk",5,IF(F19="Very high risk",6, ""))))))</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="H19" s="7">
-        <f>IF(F19="Very low risk",0.75,IF(F19="Low risk",0.85,IF(F19="Intermediate risk",1,IF(F19="Moderately high risk",1.1,IF(F19="High risk",1.15,IF(F19="Very high risk",1.25, ""))))))</f>
+        <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="I19"/>
@@ -1657,11 +1653,11 @@
         <v>Low risk</v>
       </c>
       <c r="G20" s="8">
-        <f>IF(F20="Very low risk",1,IF(F20="Low risk",2,IF(F20="Intermediate risk",3,IF(F20="Moderately high risk",4,IF(F20="High risk",5,IF(F20="Very high risk",6, ""))))))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="H20" s="7">
-        <f>IF(F20="Very low risk",0.75,IF(F20="Low risk",0.85,IF(F20="Intermediate risk",1,IF(F20="Moderately high risk",1.1,IF(F20="High risk",1.15,IF(F20="Very high risk",1.25, ""))))))</f>
+        <f t="shared" si="1"/>
         <v>0.85</v>
       </c>
       <c r="I20"/>
@@ -1685,11 +1681,11 @@
         <v>Moderately high risk</v>
       </c>
       <c r="G21" s="8">
-        <f>IF(F21="Very low risk",1,IF(F21="Low risk",2,IF(F21="Intermediate risk",3,IF(F21="Moderately high risk",4,IF(F21="High risk",5,IF(F21="Very high risk",6, ""))))))</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="H21" s="7">
-        <f>IF(F21="Very low risk",0.75,IF(F21="Low risk",0.85,IF(F21="Intermediate risk",1,IF(F21="Moderately high risk",1.1,IF(F21="High risk",1.15,IF(F21="Very high risk",1.25, ""))))))</f>
+        <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="I21"/>
@@ -1713,11 +1709,11 @@
         <v>Moderately high risk</v>
       </c>
       <c r="G22" s="8">
-        <f>IF(F22="Very low risk",1,IF(F22="Low risk",2,IF(F22="Intermediate risk",3,IF(F22="Moderately high risk",4,IF(F22="High risk",5,IF(F22="Very high risk",6, ""))))))</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="H22" s="7">
-        <f>IF(F22="Very low risk",0.75,IF(F22="Low risk",0.85,IF(F22="Intermediate risk",1,IF(F22="Moderately high risk",1.1,IF(F22="High risk",1.15,IF(F22="Very high risk",1.25, ""))))))</f>
+        <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="I22"/>
@@ -1741,11 +1737,11 @@
         <v>Intermediate risk</v>
       </c>
       <c r="G23" s="8">
-        <f>IF(F23="Very low risk",1,IF(F23="Low risk",2,IF(F23="Intermediate risk",3,IF(F23="Moderately high risk",4,IF(F23="High risk",5,IF(F23="Very high risk",6, ""))))))</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="H23" s="7">
-        <f>IF(F23="Very low risk",0.75,IF(F23="Low risk",0.85,IF(F23="Intermediate risk",1,IF(F23="Moderately high risk",1.1,IF(F23="High risk",1.15,IF(F23="Very high risk",1.25, ""))))))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="I23"/>
@@ -1769,11 +1765,11 @@
         <v>Intermediate risk</v>
       </c>
       <c r="G24" s="8">
-        <f>IF(F24="Very low risk",1,IF(F24="Low risk",2,IF(F24="Intermediate risk",3,IF(F24="Moderately high risk",4,IF(F24="High risk",5,IF(F24="Very high risk",6, ""))))))</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="H24" s="7">
-        <f>IF(F24="Very low risk",0.75,IF(F24="Low risk",0.85,IF(F24="Intermediate risk",1,IF(F24="Moderately high risk",1.1,IF(F24="High risk",1.15,IF(F24="Very high risk",1.25, ""))))))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="I24"/>
@@ -1797,11 +1793,11 @@
         <v>Intermediate risk</v>
       </c>
       <c r="G25" s="8">
-        <f>IF(F25="Very low risk",1,IF(F25="Low risk",2,IF(F25="Intermediate risk",3,IF(F25="Moderately high risk",4,IF(F25="High risk",5,IF(F25="Very high risk",6, ""))))))</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="H25" s="7">
-        <f>IF(F25="Very low risk",0.75,IF(F25="Low risk",0.85,IF(F25="Intermediate risk",1,IF(F25="Moderately high risk",1.1,IF(F25="High risk",1.15,IF(F25="Very high risk",1.25, ""))))))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="I25"/>
@@ -1825,11 +1821,11 @@
         <v>Moderately high risk</v>
       </c>
       <c r="G26" s="8">
-        <f>IF(F26="Very low risk",1,IF(F26="Low risk",2,IF(F26="Intermediate risk",3,IF(F26="Moderately high risk",4,IF(F26="High risk",5,IF(F26="Very high risk",6, ""))))))</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="H26" s="7">
-        <f>IF(F26="Very low risk",0.75,IF(F26="Low risk",0.85,IF(F26="Intermediate risk",1,IF(F26="Moderately high risk",1.1,IF(F26="High risk",1.15,IF(F26="Very high risk",1.25, ""))))))</f>
+        <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="I26"/>
@@ -1853,11 +1849,11 @@
         <v>Moderately high risk</v>
       </c>
       <c r="G27" s="8">
-        <f>IF(F27="Very low risk",1,IF(F27="Low risk",2,IF(F27="Intermediate risk",3,IF(F27="Moderately high risk",4,IF(F27="High risk",5,IF(F27="Very high risk",6, ""))))))</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="H27" s="7">
-        <f>IF(F27="Very low risk",0.75,IF(F27="Low risk",0.85,IF(F27="Intermediate risk",1,IF(F27="Moderately high risk",1.1,IF(F27="High risk",1.15,IF(F27="Very high risk",1.25, ""))))))</f>
+        <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="I27"/>
@@ -1881,11 +1877,11 @@
         <v>Moderately high risk</v>
       </c>
       <c r="G28" s="8">
-        <f>IF(F28="Very low risk",1,IF(F28="Low risk",2,IF(F28="Intermediate risk",3,IF(F28="Moderately high risk",4,IF(F28="High risk",5,IF(F28="Very high risk",6, ""))))))</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="H28" s="7">
-        <f>IF(F28="Very low risk",0.75,IF(F28="Low risk",0.85,IF(F28="Intermediate risk",1,IF(F28="Moderately high risk",1.1,IF(F28="High risk",1.15,IF(F28="Very high risk",1.25, ""))))))</f>
+        <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="I28"/>
@@ -1909,11 +1905,11 @@
         <v>Moderately high risk</v>
       </c>
       <c r="G29" s="8">
-        <f>IF(F29="Very low risk",1,IF(F29="Low risk",2,IF(F29="Intermediate risk",3,IF(F29="Moderately high risk",4,IF(F29="High risk",5,IF(F29="Very high risk",6, ""))))))</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="H29" s="7">
-        <f>IF(F29="Very low risk",0.75,IF(F29="Low risk",0.85,IF(F29="Intermediate risk",1,IF(F29="Moderately high risk",1.1,IF(F29="High risk",1.15,IF(F29="Very high risk",1.25, ""))))))</f>
+        <f t="shared" si="1"/>
         <v>1.1000000000000001</v>
       </c>
     </row>
@@ -2184,23 +2180,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100086DC0FFDEFA864DA147FFDEA823F2EE" ma:contentTypeVersion="3" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="efa000e167d9ce5db8cd2eb5b6f87cd4">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c41a64fd-65ba-4a6e-8004-8ade4c8fdb39" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f94584ddf2c7798ba84aeef6e679263" ns2:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100086DC0FFDEFA864DA147FFDEA823F2EE" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="39870545afabb502c4050089500bd5b6">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c41a64fd-65ba-4a6e-8004-8ade4c8fdb39" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bb2a11c505461e40f497f8b9cdcbcf5" ns2:_="">
     <xsd:import namespace="c41a64fd-65ba-4a6e-8004-8ade4c8fdb39"/>
     <xsd:element name="properties">
       <xsd:complexType>
@@ -2246,8 +2227,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo di contenuto"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titolo"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -2336,20 +2317,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC3B53C7-F1BC-413A-A4D7-DC6FF0496D9B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c41a64fd-65ba-4a6e-8004-8ade4c8fdb39"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B735943-41BA-429C-8E3B-7819DE4CC8FD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2361,19 +2345,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E801DC2-9584-4903-BB94-41DE98034CC9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC3B53C7-F1BC-413A-A4D7-DC6FF0496D9B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="c41a64fd-65ba-4a6e-8004-8ade4c8fdb39"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="c41a64fd-65ba-4a6e-8004-8ade4c8fdb39"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/processed/Sector Risk Multiplier.xlsx
+++ b/data/processed/Sector Risk Multiplier.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bocconi.sharepoint.com/sites/Geopolitics-DataGroup1/Documenti condivisi/General/Final Dataset - CGPR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{C119449E-6502-3D40-900F-2253E9344213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DF10385-120A-2A45-93B7-7AA9827A85D3}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{C119449E-6502-3D40-900F-2253E9344213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0780D0DC-50D8-7644-9934-F9CFC6A28B08}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="18000" xr2:uid="{39628D33-4669-BF42-B458-9D95EBDC9FA0}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{39628D33-4669-BF42-B458-9D95EBDC9FA0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sector Risk Multiplier" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="115">
   <si>
     <r>
       <rPr>
@@ -340,12 +340,81 @@
   <si>
     <t>Unregulated power and gas</t>
   </si>
+  <si>
+    <t>Leonardo</t>
+  </si>
+  <si>
+    <t>Pfizer</t>
+  </si>
+  <si>
+    <t>Prysmian</t>
+  </si>
+  <si>
+    <t>Unicredit</t>
+  </si>
+  <si>
+    <t>Campari</t>
+  </si>
+  <si>
+    <t>Moncler</t>
+  </si>
+  <si>
+    <t>Ferrari</t>
+  </si>
+  <si>
+    <t>Alibaba</t>
+  </si>
+  <si>
+    <t>Nestlè</t>
+  </si>
+  <si>
+    <t>Gazprom</t>
+  </si>
+  <si>
+    <t>Novartis</t>
+  </si>
+  <si>
+    <t>Moderna</t>
+  </si>
+  <si>
+    <t>HSBC</t>
+  </si>
+  <si>
+    <t>Walmart</t>
+  </si>
+  <si>
+    <t>Unilever</t>
+  </si>
+  <si>
+    <t>Coca-Cola</t>
+  </si>
+  <si>
+    <t>Caterpillar</t>
+  </si>
+  <si>
+    <t>Tesla</t>
+  </si>
+  <si>
+    <t>Alphabet</t>
+  </si>
+  <si>
+    <t>Saudi Aramco</t>
+  </si>
+  <si>
+    <t>Shell</t>
+  </si>
+  <si>
+    <t>Chevron</t>
+  </si>
+  <si>
+    <t>ExxonMobil</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -420,8 +489,24 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -434,8 +519,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -473,11 +564,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -491,9 +604,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="11">
     <dxf>
@@ -818,8 +939,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EB4E3128-EB28-7849-AE77-5A030531D3E5}" name="Tabella2" displayName="Tabella2" ref="D4:H29" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
-  <autoFilter ref="D4:H29" xr:uid="{EB4E3128-EB28-7849-AE77-5A030531D3E5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EB4E3128-EB28-7849-AE77-5A030531D3E5}" name="Tabella2" displayName="Tabella2" ref="D4:H52" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="D4:H52" xr:uid="{EB4E3128-EB28-7849-AE77-5A030531D3E5}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D5:H29">
     <sortCondition ref="D4:D29"/>
   </sortState>
@@ -1920,6 +2041,24 @@
       <c r="B30" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="D30" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" s="11" t="str">
+        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],Tabella1[],2)</f>
+        <v>Intermediate risk</v>
+      </c>
+      <c r="G30" s="8">
+        <f t="shared" ref="G30:G52" si="2">IF(F30="Very low risk",1,IF(F30="Low risk",2,IF(F30="Intermediate risk",3,IF(F30="Moderately high risk",4,IF(F30="High risk",5,IF(F30="Very high risk",6, ""))))))</f>
+        <v>3</v>
+      </c>
+      <c r="H30" s="12">
+        <f t="shared" ref="H30:H52" si="3">IF(F30="Very low risk",0.75,IF(F30="Low risk",0.85,IF(F30="Intermediate risk",1,IF(F30="Moderately high risk",1.1,IF(F30="High risk",1.15,IF(F30="Very high risk",1.25, ""))))))</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
@@ -1928,6 +2067,24 @@
       <c r="B31" s="3" t="s">
         <v>9</v>
       </c>
+      <c r="D31" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F31" s="11" t="str">
+        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],Tabella1[],2)</f>
+        <v>Low risk</v>
+      </c>
+      <c r="G31" s="8">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="H31" s="12">
+        <f t="shared" si="3"/>
+        <v>0.85</v>
+      </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
@@ -1936,168 +2093,546 @@
       <c r="B32" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F32" s="11" t="str">
+        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],Tabella1[],2)</f>
+        <v>Intermediate risk</v>
+      </c>
+      <c r="G32" s="8">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H32" s="12">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>70</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D33" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F33" s="11" t="str">
+        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],Tabella1[],2)</f>
+        <v>Moderately high risk</v>
+      </c>
+      <c r="G33" s="8">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="H33" s="12">
+        <f t="shared" si="3"/>
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>72</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D34" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F34" s="11" t="str">
+        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],Tabella1[],2)</f>
+        <v>Low risk</v>
+      </c>
+      <c r="G34" s="8">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="H34" s="12">
+        <f t="shared" si="3"/>
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>73</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D35" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F35" s="11" t="str">
+        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],Tabella1[],2)</f>
+        <v>Intermediate risk</v>
+      </c>
+      <c r="G35" s="8">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H35" s="12">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>74</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D36" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F36" s="11" t="str">
+        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],Tabella1[],2)</f>
+        <v>Moderately high risk</v>
+      </c>
+      <c r="G36" s="8">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="H36" s="12">
+        <f t="shared" si="3"/>
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>75</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D37" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F37" s="11" t="str">
+        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],Tabella1[],2)</f>
+        <v>Intermediate risk</v>
+      </c>
+      <c r="G37" s="8">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H37" s="12">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>76</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D38" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F38" s="11" t="str">
+        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],Tabella1[],2)</f>
+        <v>Low risk</v>
+      </c>
+      <c r="G38" s="8">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="H38" s="12">
+        <f t="shared" si="3"/>
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D39" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F39" s="11" t="str">
+        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],Tabella1[],2)</f>
+        <v>Moderately high risk</v>
+      </c>
+      <c r="G39" s="8">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="H39" s="12">
+        <f t="shared" si="3"/>
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>78</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D40" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F40" s="11" t="str">
+        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],Tabella1[],2)</f>
+        <v>Low risk</v>
+      </c>
+      <c r="G40" s="8">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="H40" s="12">
+        <f t="shared" si="3"/>
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D41" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F41" s="11" t="str">
+        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],Tabella1[],2)</f>
+        <v>Low risk</v>
+      </c>
+      <c r="G41" s="8">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="H41" s="12">
+        <f t="shared" si="3"/>
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>79</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D42" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F42" s="11" t="str">
+        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],Tabella1[],2)</f>
+        <v>Moderately high risk</v>
+      </c>
+      <c r="G42" s="8">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="H42" s="12">
+        <f t="shared" si="3"/>
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D43" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F43" s="11" t="str">
+        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],Tabella1[],2)</f>
+        <v>Intermediate risk</v>
+      </c>
+      <c r="G43" s="8">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H43" s="12">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>80</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D44" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F44" s="11" t="str">
+        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],Tabella1[],2)</f>
+        <v>Low risk</v>
+      </c>
+      <c r="G44" s="8">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="H44" s="12">
+        <f t="shared" si="3"/>
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>81</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D45" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F45" s="11" t="str">
+        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],Tabella1[],2)</f>
+        <v>Low risk</v>
+      </c>
+      <c r="G45" s="8">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="H45" s="12">
+        <f t="shared" si="3"/>
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D46" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F46" s="11" t="str">
+        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],Tabella1[],2)</f>
+        <v>Intermediate risk</v>
+      </c>
+      <c r="G46" s="8">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H46" s="12">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D47" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F47" s="11" t="str">
+        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],Tabella1[],2)</f>
+        <v>Moderately high risk</v>
+      </c>
+      <c r="G47" s="8">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="H47" s="12">
+        <f t="shared" si="3"/>
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>84</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D48" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F48" s="11" t="str">
+        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],Tabella1[],2)</f>
+        <v>Intermediate risk</v>
+      </c>
+      <c r="G48" s="8">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="H48" s="12">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D49" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F49" s="11" t="str">
+        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],Tabella1[],2)</f>
+        <v>Moderately high risk</v>
+      </c>
+      <c r="G49" s="8">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="H49" s="12">
+        <f t="shared" si="3"/>
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>85</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D50" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F50" s="11" t="str">
+        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],Tabella1[],2)</f>
+        <v>Moderately high risk</v>
+      </c>
+      <c r="G50" s="8">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="H50" s="12">
+        <f t="shared" si="3"/>
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D51" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F51" s="11" t="str">
+        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],Tabella1[],2)</f>
+        <v>Moderately high risk</v>
+      </c>
+      <c r="G51" s="8">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="H51" s="12">
+        <f t="shared" si="3"/>
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D52" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="E52" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="F52" s="14" t="str">
+        <f xml:space="preserve"> VLOOKUP(Tabella2[[#This Row],[Sector]],Tabella1[],2)</f>
+        <v>Moderately high risk</v>
+      </c>
+      <c r="G52" s="13">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="H52" s="15">
+        <f t="shared" si="3"/>
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>86</v>
       </c>
@@ -2105,7 +2640,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>87</v>
       </c>
@@ -2113,7 +2648,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>89</v>
       </c>
@@ -2121,7 +2656,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>90</v>
       </c>
@@ -2129,7 +2664,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>91</v>
       </c>
@@ -2142,7 +2677,7 @@
     <mergeCell ref="A1:D2"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
-  <conditionalFormatting sqref="H5:H29">
+  <conditionalFormatting sqref="H5:H52">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -2180,8 +2715,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100086DC0FFDEFA864DA147FFDEA823F2EE" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="39870545afabb502c4050089500bd5b6">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c41a64fd-65ba-4a6e-8004-8ade4c8fdb39" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bb2a11c505461e40f497f8b9cdcbcf5" ns2:_="">
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100086DC0FFDEFA864DA147FFDEA823F2EE" ma:contentTypeVersion="3" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="efa000e167d9ce5db8cd2eb5b6f87cd4">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c41a64fd-65ba-4a6e-8004-8ade4c8fdb39" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1f94584ddf2c7798ba84aeef6e679263" ns2:_="">
     <xsd:import namespace="c41a64fd-65ba-4a6e-8004-8ade4c8fdb39"/>
     <xsd:element name="properties">
       <xsd:complexType>
@@ -2227,8 +2771,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo di contenuto"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titolo"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -2317,15 +2861,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -2333,10 +2868,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B735943-41BA-429C-8E3B-7819DE4CC8FD}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A0047C2-3AA2-4380-A263-E8F6A4179711}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -2344,18 +2875,22 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65C7DB2B-ED72-4A45-9CDA-C30219DC14E3}"/>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC3B53C7-F1BC-413A-A4D7-DC6FF0496D9B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="c41a64fd-65ba-4a6e-8004-8ade4c8fdb39"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>